--- a/public/HVH_mo_tai_khoan.xlsx
+++ b/public/HVH_mo_tai_khoan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\CocCoc_Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1382B6C2-178F-48A6-A3C6-B4C3F6D13204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BF14BC-F760-439C-AF49-ED1D473C9ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{A7A1BDD3-3C63-4DDF-B4FA-8B5A55D06281}"/>
   </bookViews>
@@ -440,11 +440,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -841,9 +841,9 @@
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="11"/>
       <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="12"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
     </row>
